--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A1104B-7FA7-4B78-A4C8-27712886F743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A633AF-EF99-41F4-BD0B-A3DC70A45AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8415" yWindow="5190" windowWidth="26820" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="2280" windowWidth="26130" windowHeight="17670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,7 +66,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>确定界面的模块排版</t>
+    <t>最小化的AI生成的游戏框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI桌面框体入口出口实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI桌面实际打包桌面测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steam云存档</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -90,7 +102,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,6 +112,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -116,12 +140,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -404,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
@@ -432,32 +462,79 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="3">
         <v>20250902</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20250922</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20250923</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3">
+        <v>20250923</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A633AF-EF99-41F4-BD0B-A3DC70A45AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8C185E-8479-4D7A-854D-FA26879AFF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6180" yWindow="2280" windowWidth="26130" windowHeight="17670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,6 +79,14 @@
   </si>
   <si>
     <t>Steam云存档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小案例先跑通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>思考：商业模式 开发重点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -102,7 +110,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,6 +135,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -140,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -152,6 +166,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -434,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
@@ -534,7 +551,20 @@
         <v>5</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8C185E-8479-4D7A-854D-FA26879AFF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F12D6-7D94-4018-80F6-AEEA8A483FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="2280" windowWidth="26130" windowHeight="17670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10755" yWindow="3540" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>思考：商业模式 开发重点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可创建一条任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steam 存档 读取一条任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文字体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -451,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
@@ -566,6 +578,45 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F12D6-7D94-4018-80F6-AEEA8A483FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5A3BAF-E7F1-4761-A6D0-D4C45F9DF6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10755" yWindow="3540" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,6 +99,22 @@
   </si>
   <si>
     <t>中文字体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可创建一件商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持久化用户信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持久化任务信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持久化商品信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
@@ -592,30 +608,76 @@
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5A3BAF-E7F1-4761-A6D0-D4C45F9DF6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A90CE05-8D9C-4C02-B38A-77788FDEE17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10755" yWindow="3540" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="2655" windowWidth="28800" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,15 +106,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>持久化用户信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持久化任务信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持久化商品信息</t>
+    <t>持久化用户信息、任务信息、商品信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -479,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
@@ -634,17 +626,17 @@
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -656,28 +648,6 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fork\DesireStore\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A90CE05-8D9C-4C02-B38A-77788FDEE17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54388DDE-5CA6-434F-97D7-702A0BA1039B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="2655" windowWidth="28800" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10755" yWindow="3540" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -639,15 +639,15 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54388DDE-5CA6-434F-97D7-702A0BA1039B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEB2BDB-8CB6-48EA-ADE6-0006A98A8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10755" yWindow="3540" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8085" yWindow="5055" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="结构" sheetId="2" r:id="rId1"/>
+    <sheet name="任务" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">任务!$D$1:$D$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,6 +108,170 @@
   </si>
   <si>
     <t>持久化用户信息、任务信息、商品信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝南书房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>称号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昵称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财富</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evoreek野鹤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录用户的ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荣誉勋章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欲望币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金钱财富</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标生命体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉淀能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心原则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀怪物获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀怪物获得、完成任务获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀怪物条件之一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定任务（打卡）/自定义标签任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比如古琴技能条件：物品：古琴 熟练度：3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实物物品/消耗物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限时怪物/永久怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可完成任务购买物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可完成任务购买查看物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +279,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,8 +294,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +335,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -174,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -190,6 +370,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,6 +659,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD925259-6BD9-4533-9B8B-B307F6DB1C23}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEB2BDB-8CB6-48EA-ADE6-0006A98A8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA95E7AB-FE6B-465F-B578-2FA7072D255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8085" yWindow="5055" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10260" yWindow="3270" windowWidth="21315" windowHeight="14400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -883,7 +883,7 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.375" style="1" customWidth="1"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA95E7AB-FE6B-465F-B578-2FA7072D255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36019F9-2B23-4A2F-B88B-5F62D4F5F880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="3270" windowWidth="21315" windowHeight="14400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10260" yWindow="3270" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -272,6 +272,10 @@
   </si>
   <si>
     <t>背包信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可查看已完成任务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -880,7 +884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1053,10 +1057,23 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36019F9-2B23-4A2F-B88B-5F62D4F5F880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958721DA-D5F4-4B32-A5DB-B510B20E065B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="3270" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8745" yWindow="2175" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -358,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -379,9 +379,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -667,6 +664,12 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="6" max="6" width="12.25" customWidth="1"/>
     <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -709,7 +712,7 @@
       <c r="H4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>59</v>
       </c>
     </row>
@@ -721,7 +724,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
@@ -731,7 +734,7 @@
         <v>33</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -740,7 +743,7 @@
       <c r="C7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958721DA-D5F4-4B32-A5DB-B510B20E065B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8139BB1F-A356-4766-B337-ADBE47C3A584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8745" yWindow="2175" windowWidth="21315" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18975" yWindow="3645" windowWidth="16245" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,74 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用户信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>称号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设计结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>昵称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财富</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>核心模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>核心数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>知识库信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>知识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,91 +123,170 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>记录用户的ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荣誉勋章</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>欲望币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金钱财富</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拆分任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最小物品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标生命体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉淀能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>知识库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>核心原则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀怪物获得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀怪物获得、完成任务获得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀怪物条件之一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定任务（打卡）/自定义标签任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比如古琴技能条件：物品：古琴 熟练度：3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实物物品/消耗物品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>限时怪物/永久怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关联</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可完成任务购买物品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可完成任务购买查看物品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>背包信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可查看已完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欲望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人脉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昵称、交互点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店、成就、资产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>思维、知识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信息、关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术、技能、产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五行对应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财才</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>印枭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比劫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚浮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>得令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不弱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成就</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成就设定引导任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产储蓄和调配</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>购买商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昵称、交互点显示</t>
+  </si>
+  <si>
+    <t>昵称、交互点显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行获取交互点 默认显示待执行任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,7 +294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,8 +318,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,7 +360,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFAFAF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -376,10 +401,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -387,6 +421,15 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFAFAF"/>
+      <color rgb="FFFF1919"/>
+      <color rgb="FFFF8585"/>
+      <color rgb="FFFF4B4B"/>
+      <color rgb="FFFF7C80"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -661,227 +704,483 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD925259-6BD9-4533-9B8B-B307F6DB1C23}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
-    <col min="6" max="6" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="B13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="C16" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I7"/>
+  <mergeCells count="6">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1067,10 +1366,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>6</v>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fork\DesireStore\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8139BB1F-A356-4766-B337-ADBE47C3A584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A2C7D6-D1F9-4608-81C4-BF0E84386AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18975" yWindow="3645" windowWidth="16245" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7110" yWindow="3615" windowWidth="23760" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,6 +287,14 @@
   </si>
   <si>
     <t>完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建和查看任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建和查看成就</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -294,7 +302,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,8 +334,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,6 +387,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -383,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -402,18 +425,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -704,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD925259-6BD9-4533-9B8B-B307F6DB1C23}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -712,13 +747,14 @@
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.375" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
@@ -727,10 +763,10 @@
       </c>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -747,7 +783,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -765,20 +801,20 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F5" s="6"/>
@@ -787,20 +823,20 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6"/>
@@ -809,7 +845,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
@@ -831,7 +867,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
@@ -853,7 +889,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
@@ -875,7 +911,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -887,145 +923,162 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="15" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D14" s="12"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B17" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C17" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="7" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1037,7 +1090,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1049,7 +1102,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1061,7 +1114,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1073,7 +1126,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1085,55 +1138,61 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1169,14 +1228,22 @@
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C15:D15"/>
+  <mergeCells count="8">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/任务单.xlsx
+++ b/Assets/任务单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Fork\DesireStore\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A2C7D6-D1F9-4608-81C4-BF0E84386AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068A530D-44FF-485A-B228-13A65245B75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7110" yWindow="3615" windowWidth="23760" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8295" yWindow="3585" windowWidth="23760" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
   <si>
     <t>内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -429,25 +429,25 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -930,10 +930,10 @@
       <c r="B11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="9" t="s">
         <v>63</v>
       </c>
@@ -942,17 +942,17 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="10" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="6"/>
@@ -963,17 +963,17 @@
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -982,17 +982,17 @@
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -1001,17 +1001,17 @@
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="6"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -1020,17 +1020,17 @@
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="6"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1039,17 +1039,17 @@
       <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="14" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="10" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="6"/>
@@ -1060,17 +1060,19 @@
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
